--- a/KiCAD-PCB/Version20260523/BOM_ESP32C6_gasometer.xlsx
+++ b/KiCAD-PCB/Version20260523/BOM_ESP32C6_gasometer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekte\gas-o-meter2\KiCAD-PCB\Version20260523\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C596AE81-8934-47B6-8709-4D535FC4699B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6F0B6E-DAFC-4B8C-8178-FFEE66F5D538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25650" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="570" windowWidth="25650" windowHeight="14520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_ESP32C6_gasometer" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Reference</t>
   </si>
@@ -127,10 +127,19 @@
     <t>Generic connector, single row, 01x02 // Batterie</t>
   </si>
   <si>
-    <t>JST-SH 1.25 2pin plug/socket</t>
-  </si>
-  <si>
     <t>Generic connector, single row, 01x02 // Reed</t>
+  </si>
+  <si>
+    <t>JST-XH 1.25 2pin socket</t>
+  </si>
+  <si>
+    <t>JST-XH 1.25 2pin plug</t>
+  </si>
+  <si>
+    <t>Li-Polymer Battery  52x34x5,0mm</t>
+  </si>
+  <si>
+    <t>LiPo 1000mAh 523450</t>
   </si>
 </sst>
 </file>
@@ -491,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -526,10 +535,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -543,7 +552,7 @@
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -670,6 +679,20 @@
       </c>
       <c r="C12" t="s">
         <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
